--- a/public/downloads/公开名单-CPI-离岸-FATF-20260817.xlsx
+++ b/public/downloads/公开名单-CPI-离岸-FATF-20260817.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CPI 2024" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CPI 2025" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offshore Centres 离岸中心" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FATF 黑灰名单" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D182"/>
+  <dimension ref="A1:D184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -492,7 +492,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>来源: Transparency International — Corruption Perceptions Index 2024 (https://www.transparency.org/en/cpi/2024) · 0-100，分数越低越腐败 · 红底 = 低于建议阈值 31（待法务确认） · 抓取: 2026-08-17</t>
+          <t>来源: Transparency International — Corruption Perceptions Index 2025 (https://www.transparency.org/en/cpi/2025) · 0-100，分数越低越腐败 · 红底 = 低于建议阈值 31（待法务确认） · 抓取: 2026-08-17</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D3" s="5" t="n"/>
     </row>
@@ -573,17 +573,17 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
@@ -593,21 +593,21 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D9" s="5" t="n"/>
     </row>
@@ -625,17 +625,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
@@ -677,21 +677,21 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
@@ -705,11 +705,11 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
@@ -719,25 +719,25 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
@@ -751,11 +751,11 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D19" s="5" t="n"/>
     </row>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D20" s="5" t="n"/>
     </row>
@@ -779,11 +779,11 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Seychelles</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D21" s="5" t="n"/>
     </row>
@@ -793,31 +793,31 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D22" s="5" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
@@ -831,25 +831,25 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Barbados</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D25" s="5" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Barbados</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
@@ -859,43 +859,43 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Seychelles</t>
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D27" s="5" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D28" s="5" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D29" s="5" t="n"/>
     </row>
@@ -905,7 +905,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Bahamas</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
@@ -915,25 +915,25 @@
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Bahamas</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D31" s="5" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
@@ -943,21 +943,21 @@
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Korea, South</t>
+          <t>Brunei Darussalam</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D33" s="5" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
@@ -971,11 +971,11 @@
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Korea, South</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
@@ -985,7 +985,7 @@
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
@@ -1013,25 +1013,25 @@
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Dominica</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D38" s="5" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Dominica</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
@@ -1041,7 +1041,7 @@
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
@@ -1049,17 +1049,17 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D40" s="5" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
@@ -1069,7 +1069,7 @@
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
@@ -1083,25 +1083,25 @@
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D43" s="5" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Costa Rica</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
@@ -1111,39 +1111,39 @@
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D45" s="5" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D46" s="5" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Costa Rica</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Grenada</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Grenada</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
@@ -1195,21 +1195,21 @@
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Cyprus</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D51" s="5" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
@@ -1223,11 +1223,11 @@
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
@@ -1245,17 +1245,17 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D54" s="5" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Bahrain</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
@@ -1265,29 +1265,29 @@
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D56" s="5" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Oman</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D57" s="5" t="n"/>
     </row>
@@ -1297,21 +1297,21 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>Mauritius</t>
+          <t>Bahrain</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D58" s="5" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
@@ -1321,11 +1321,11 @@
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>Vanuatu</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
@@ -1335,25 +1335,25 @@
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D61" s="5" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
@@ -1363,21 +1363,21 @@
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Mauritius</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D63" s="5" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="4" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D64" s="5" t="n"/>
     </row>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Vanuatu</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
@@ -1475,25 +1475,25 @@
     </row>
     <row r="71">
       <c r="A71" s="4" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D71" s="5" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="4" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>Côte d'Ivoire</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="C72" s="4" t="n">
@@ -1503,11 +1503,11 @@
     </row>
     <row r="73">
       <c r="A73" s="4" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Sao Tome and Principe</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="C73" s="4" t="n">
@@ -1517,11 +1517,11 @@
     </row>
     <row r="74">
       <c r="A74" s="4" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Sao Tome and Principe</t>
         </is>
       </c>
       <c r="C74" s="4" t="n">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>Kosovo</t>
+          <t>Solomon Islands</t>
         </is>
       </c>
       <c r="C76" s="4" t="n">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C78" s="4" t="n">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Cote d'Ivoire</t>
         </is>
       </c>
       <c r="C79" s="4" t="n">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>Moldova</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="C80" s="4" t="n">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>Solomon Islands</t>
+          <t>Kosovo</t>
         </is>
       </c>
       <c r="C81" s="4" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>Albania</t>
+          <t>Moldova</t>
         </is>
       </c>
       <c r="C82" s="4" t="n">
@@ -1643,25 +1643,25 @@
     </row>
     <row r="83">
       <c r="A83" s="4" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D83" s="5" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="4" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>Burkina Faso</t>
+          <t>Trinidad and Tobago</t>
         </is>
       </c>
       <c r="C84" s="4" t="n">
@@ -1671,11 +1671,11 @@
     </row>
     <row r="85">
       <c r="A85" s="4" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>Cuba</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C85" s="4" t="n">
@@ -1685,67 +1685,67 @@
     </row>
     <row r="86">
       <c r="A86" s="4" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D86" s="5" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="4" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Burkina Faso</t>
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D87" s="5" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="4" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Cuba</t>
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D88" s="5" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="4" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>Trinidad and Tobago</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D89" s="5" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="4" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="C90" s="4" t="n">
@@ -1755,7 +1755,7 @@
     </row>
     <row r="91">
       <c r="A91" s="4" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
@@ -1769,11 +1769,11 @@
     </row>
     <row r="92">
       <c r="A92" s="4" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>Suriname</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="C92" s="4" t="n">
@@ -1783,25 +1783,25 @@
     </row>
     <row r="93">
       <c r="A93" s="4" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Albania</t>
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D93" s="5" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="4" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C94" s="4" t="n">
@@ -1811,11 +1811,11 @@
     </row>
     <row r="95">
       <c r="A95" s="4" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Maldives</t>
         </is>
       </c>
       <c r="C95" s="4" t="n">
@@ -1825,11 +1825,11 @@
     </row>
     <row r="96">
       <c r="A96" s="4" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="C96" s="4" t="n">
@@ -1839,11 +1839,11 @@
     </row>
     <row r="97">
       <c r="A97" s="4" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="C97" s="4" t="n">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>Gambia</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="C98" s="4" t="n">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="C99" s="4" t="n">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>Maldives</t>
+          <t>Suriname</t>
         </is>
       </c>
       <c r="C100" s="4" t="n">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="C101" s="4" t="n">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="C102" s="4" t="n">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Gambia</t>
         </is>
       </c>
       <c r="C103" s="4" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="C105" s="4" t="n">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="C106" s="4" t="n">
@@ -1979,21 +1979,21 @@
     </row>
     <row r="107">
       <c r="A107" s="4" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>Belize</t>
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D107" s="5" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="4" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D108" s="5" t="n"/>
     </row>
@@ -2011,11 +2011,11 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D109" s="5" t="n"/>
     </row>
@@ -2025,21 +2025,21 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Sri Lanka</t>
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D110" s="5" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="4" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>Malawi</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C111" s="4" t="n">
@@ -2049,11 +2049,11 @@
     </row>
     <row r="112">
       <c r="A112" s="4" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="C112" s="4" t="n">
@@ -2063,11 +2063,11 @@
     </row>
     <row r="113">
       <c r="A113" s="4" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>Niger</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="C113" s="4" t="n">
@@ -2077,11 +2077,11 @@
     </row>
     <row r="114">
       <c r="A114" s="4" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Laos</t>
         </is>
       </c>
       <c r="C114" s="4" t="n">
@@ -2091,11 +2091,11 @@
     </row>
     <row r="115">
       <c r="A115" s="4" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="C115" s="4" t="n">
@@ -2105,39 +2105,39 @@
     </row>
     <row r="116">
       <c r="A116" s="4" t="n">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>Belarus</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D116" s="5" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="4" t="n">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Sierra Leone</t>
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D117" s="5" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="4" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>Laos</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="C118" s="4" t="n">
@@ -2147,11 +2147,11 @@
     </row>
     <row r="119">
       <c r="A119" s="4" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>Mongolia</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="C119" s="4" t="n">
@@ -2161,11 +2161,11 @@
     </row>
     <row r="120">
       <c r="A120" s="4" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="C120" s="4" t="n">
@@ -2175,11 +2175,11 @@
     </row>
     <row r="121">
       <c r="A121" s="4" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="C121" s="4" t="n">
@@ -2189,25 +2189,25 @@
     </row>
     <row r="122">
       <c r="A122" s="4" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>Sierra Leone</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D122" s="5" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="4" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>El Salvador</t>
         </is>
       </c>
       <c r="C123" s="4" t="n">
@@ -2217,11 +2217,11 @@
     </row>
     <row r="124">
       <c r="A124" s="4" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="C124" s="4" t="n">
@@ -2231,11 +2231,11 @@
     </row>
     <row r="125">
       <c r="A125" s="4" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="C125" s="4" t="n">
@@ -2245,53 +2245,53 @@
     </row>
     <row r="126">
       <c r="A126" s="4" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Belarus</t>
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D126" s="5" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="4" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Djibouti</t>
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D127" s="5" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="4" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Mongolia</t>
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D128" s="5" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="4" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>Djibouti</t>
+          <t>Niger</t>
         </is>
       </c>
       <c r="C129" s="4" t="n">
@@ -2301,11 +2301,11 @@
     </row>
     <row r="130">
       <c r="A130" s="4" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>Papua New Guinea</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="C130" s="4" t="n">
@@ -2315,11 +2315,11 @@
     </row>
     <row r="131">
       <c r="A131" s="4" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="C131" s="4" t="n">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="B132" s="7" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Azerbaijan</t>
         </is>
       </c>
       <c r="C132" s="6" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="B133" s="7" t="inlineStr">
         <is>
-          <t>El Salvador</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="C133" s="6" t="n">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="B134" s="7" t="inlineStr">
         <is>
-          <t>Mauritania</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C134" s="6" t="n">
@@ -2383,15 +2383,15 @@
     </row>
     <row r="135">
       <c r="A135" s="6" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B135" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Mauritania</t>
         </is>
       </c>
       <c r="C135" s="6" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
@@ -2401,15 +2401,15 @@
     </row>
     <row r="136">
       <c r="A136" s="6" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B136" s="7" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="C136" s="6" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
@@ -2423,11 +2423,11 @@
       </c>
       <c r="B137" s="7" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="C137" s="6" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
@@ -2437,15 +2437,15 @@
     </row>
     <row r="138">
       <c r="A138" s="6" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B138" s="7" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C138" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D138" s="7" t="inlineStr">
         <is>
@@ -2455,15 +2455,15 @@
     </row>
     <row r="139">
       <c r="A139" s="6" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B139" s="7" t="inlineStr">
         <is>
-          <t>Liberia</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="C139" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D139" s="7" t="inlineStr">
         <is>
@@ -2473,15 +2473,15 @@
     </row>
     <row r="140">
       <c r="A140" s="6" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B140" s="7" t="inlineStr">
         <is>
-          <t>Mali</t>
+          <t>Liberia</t>
         </is>
       </c>
       <c r="C140" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D140" s="7" t="inlineStr">
         <is>
@@ -2491,15 +2491,15 @@
     </row>
     <row r="141">
       <c r="A141" s="6" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B141" s="7" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Mali</t>
         </is>
       </c>
       <c r="C141" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
@@ -2509,15 +2509,15 @@
     </row>
     <row r="142">
       <c r="A142" s="6" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B142" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="C142" s="6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D142" s="7" t="inlineStr">
         <is>
@@ -2527,15 +2527,15 @@
     </row>
     <row r="143">
       <c r="A143" s="6" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B143" s="7" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="C143" s="6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D143" s="7" t="inlineStr">
         <is>
@@ -2545,11 +2545,11 @@
     </row>
     <row r="144">
       <c r="A144" s="6" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B144" s="7" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C144" s="6" t="n">
@@ -2563,11 +2563,11 @@
     </row>
     <row r="145">
       <c r="A145" s="6" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B145" s="7" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Guatemala</t>
         </is>
       </c>
       <c r="C145" s="6" t="n">
@@ -2581,11 +2581,11 @@
     </row>
     <row r="146">
       <c r="A146" s="6" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B146" s="7" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Guinea</t>
         </is>
       </c>
       <c r="C146" s="6" t="n">
@@ -2599,11 +2599,11 @@
     </row>
     <row r="147">
       <c r="A147" s="6" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B147" s="7" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Kyrgyzstan</t>
         </is>
       </c>
       <c r="C147" s="6" t="n">
@@ -2617,15 +2617,15 @@
     </row>
     <row r="148">
       <c r="A148" s="6" t="n">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B148" s="7" t="inlineStr">
         <is>
-          <t>Guatemala</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="C148" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D148" s="7" t="inlineStr">
         <is>
@@ -2635,15 +2635,15 @@
     </row>
     <row r="149">
       <c r="A149" s="6" t="n">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B149" s="7" t="inlineStr">
         <is>
-          <t>Kyrgyzstan</t>
+          <t>Papua New Guinea</t>
         </is>
       </c>
       <c r="C149" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D149" s="7" t="inlineStr">
         <is>
@@ -2653,11 +2653,11 @@
     </row>
     <row r="150">
       <c r="A150" s="6" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B150" s="7" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="C150" s="6" t="n">
@@ -2671,15 +2671,15 @@
     </row>
     <row r="151">
       <c r="A151" s="6" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B151" s="7" t="inlineStr">
         <is>
-          <t>Central African Republic</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="C151" s="6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D151" s="7" t="inlineStr">
         <is>
@@ -2689,11 +2689,11 @@
     </row>
     <row r="152">
       <c r="A152" s="6" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B152" s="7" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="C152" s="6" t="n">
@@ -2707,15 +2707,15 @@
     </row>
     <row r="153">
       <c r="A153" s="6" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B153" s="7" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>Central African Republic</t>
         </is>
       </c>
       <c r="C153" s="6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D153" s="7" t="inlineStr">
         <is>
@@ -2725,15 +2725,15 @@
     </row>
     <row r="154">
       <c r="A154" s="6" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B154" s="7" t="inlineStr">
         <is>
-          <t>Congo</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="C154" s="6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D154" s="7" t="inlineStr">
         <is>
@@ -2743,11 +2743,11 @@
     </row>
     <row r="155">
       <c r="A155" s="6" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B155" s="7" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Congo</t>
         </is>
       </c>
       <c r="C155" s="6" t="n">
@@ -2761,15 +2761,15 @@
     </row>
     <row r="156">
       <c r="A156" s="6" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B156" s="7" t="inlineStr">
         <is>
-          <t>Azerbaijan</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="C156" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D156" s="7" t="inlineStr">
         <is>
@@ -2779,15 +2779,15 @@
     </row>
     <row r="157">
       <c r="A157" s="6" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B157" s="7" t="inlineStr">
         <is>
-          <t>Honduras</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="C157" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D157" s="7" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
     </row>
     <row r="158">
       <c r="A158" s="6" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B158" s="7" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="C158" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D158" s="7" t="inlineStr">
         <is>
@@ -2815,11 +2815,11 @@
     </row>
     <row r="159">
       <c r="A159" s="6" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B159" s="7" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Chad</t>
         </is>
       </c>
       <c r="C159" s="6" t="n">
@@ -2833,15 +2833,15 @@
     </row>
     <row r="160">
       <c r="A160" s="6" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B160" s="7" t="inlineStr">
         <is>
-          <t>Cambodia</t>
+          <t>Honduras</t>
         </is>
       </c>
       <c r="C160" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D160" s="7" t="inlineStr">
         <is>
@@ -2851,15 +2851,15 @@
     </row>
     <row r="161">
       <c r="A161" s="6" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B161" s="7" t="inlineStr">
         <is>
-          <t>Chad</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="C161" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D161" s="7" t="inlineStr">
         <is>
@@ -2869,15 +2869,15 @@
     </row>
     <row r="162">
       <c r="A162" s="6" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B162" s="7" t="inlineStr">
         <is>
-          <t>Comoros</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="C162" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D162" s="7" t="inlineStr">
         <is>
@@ -2887,11 +2887,11 @@
     </row>
     <row r="163">
       <c r="A163" s="6" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B163" s="7" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>Guinea Bissau</t>
         </is>
       </c>
       <c r="C163" s="6" t="n">
@@ -2905,11 +2905,11 @@
     </row>
     <row r="164">
       <c r="A164" s="6" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B164" s="7" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="C164" s="6" t="n">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="B165" s="7" t="inlineStr">
         <is>
-          <t>Democratic Republic of the Congo</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="C165" s="6" t="n">
@@ -2941,15 +2941,15 @@
     </row>
     <row r="166">
       <c r="A166" s="6" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B166" s="7" t="inlineStr">
         <is>
-          <t>Tajikistan</t>
+          <t>Comoros</t>
         </is>
       </c>
       <c r="C166" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D166" s="7" t="inlineStr">
         <is>
@@ -2959,15 +2959,15 @@
     </row>
     <row r="167">
       <c r="A167" s="6" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B167" s="7" t="inlineStr">
         <is>
-          <t>Afghanistan</t>
+          <t>Democratic Republic of the Congo</t>
         </is>
       </c>
       <c r="C167" s="6" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D167" s="7" t="inlineStr">
         <is>
@@ -2977,15 +2977,15 @@
     </row>
     <row r="168">
       <c r="A168" s="6" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B168" s="7" t="inlineStr">
         <is>
-          <t>Burundi</t>
+          <t>Tajikistan</t>
         </is>
       </c>
       <c r="C168" s="6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D168" s="7" t="inlineStr">
         <is>
@@ -2995,11 +2995,11 @@
     </row>
     <row r="169">
       <c r="A169" s="6" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B169" s="7" t="inlineStr">
         <is>
-          <t>Turkmenistan</t>
+          <t>Burundi</t>
         </is>
       </c>
       <c r="C169" s="6" t="n">
@@ -3013,15 +3013,15 @@
     </row>
     <row r="170">
       <c r="A170" s="6" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B170" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Turkmenistan</t>
         </is>
       </c>
       <c r="C170" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D170" s="7" t="inlineStr">
         <is>
@@ -3031,11 +3031,11 @@
     </row>
     <row r="171">
       <c r="A171" s="6" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B171" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Afghanistan</t>
         </is>
       </c>
       <c r="C171" s="6" t="n">
@@ -3049,15 +3049,15 @@
     </row>
     <row r="172">
       <c r="A172" s="6" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B172" s="7" t="inlineStr">
         <is>
-          <t>Korea, North</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C172" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D172" s="7" t="inlineStr">
         <is>
@@ -3067,15 +3067,15 @@
     </row>
     <row r="173">
       <c r="A173" s="6" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B173" s="7" t="inlineStr">
         <is>
-          <t>Sudan</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C173" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D173" s="7" t="inlineStr">
         <is>
@@ -3089,11 +3089,11 @@
       </c>
       <c r="B174" s="7" t="inlineStr">
         <is>
-          <t>Nicaragua</t>
+          <t>Equatorial Guinea</t>
         </is>
       </c>
       <c r="C174" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D174" s="7" t="inlineStr">
         <is>
@@ -3103,15 +3103,15 @@
     </row>
     <row r="175">
       <c r="A175" s="6" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B175" s="7" t="inlineStr">
         <is>
-          <t>Equatorial Guinea</t>
+          <t>Korea, North</t>
         </is>
       </c>
       <c r="C175" s="6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D175" s="7" t="inlineStr">
         <is>
@@ -3121,15 +3121,15 @@
     </row>
     <row r="176">
       <c r="A176" s="6" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B176" s="7" t="inlineStr">
         <is>
-          <t>Eritrea</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C176" s="6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D176" s="7" t="inlineStr">
         <is>
@@ -3139,15 +3139,15 @@
     </row>
     <row r="177">
       <c r="A177" s="6" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B177" s="7" t="inlineStr">
         <is>
-          <t>Libya</t>
+          <t>Nicaragua</t>
         </is>
       </c>
       <c r="C177" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D177" s="7" t="inlineStr">
         <is>
@@ -3157,15 +3157,15 @@
     </row>
     <row r="178">
       <c r="A178" s="6" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B178" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Sudan</t>
         </is>
       </c>
       <c r="C178" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D178" s="7" t="inlineStr">
         <is>
@@ -3179,11 +3179,11 @@
       </c>
       <c r="B179" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Eritrea</t>
         </is>
       </c>
       <c r="C179" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D179" s="7" t="inlineStr">
         <is>
@@ -3193,15 +3193,15 @@
     </row>
     <row r="180">
       <c r="A180" s="6" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B180" s="7" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Libya</t>
         </is>
       </c>
       <c r="C180" s="6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D180" s="7" t="inlineStr">
         <is>
@@ -3211,15 +3211,15 @@
     </row>
     <row r="181">
       <c r="A181" s="6" t="n">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B181" s="7" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C181" s="6" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D181" s="7" t="inlineStr">
         <is>
@@ -3233,13 +3233,49 @@
       </c>
       <c r="B182" s="7" t="inlineStr">
         <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="C182" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D182" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="6" t="n">
+        <v>181</v>
+      </c>
+      <c r="B183" s="7" t="inlineStr">
+        <is>
+          <t>Somalia</t>
+        </is>
+      </c>
+      <c r="C183" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D183" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="6" t="n">
+        <v>181</v>
+      </c>
+      <c r="B184" s="7" t="inlineStr">
+        <is>
           <t>South Sudan</t>
         </is>
       </c>
-      <c r="C182" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="D182" s="7" t="inlineStr">
+      <c r="C184" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D184" s="7" t="inlineStr">
         <is>
           <t>高风险 High-risk</t>
         </is>

--- a/public/downloads/公开名单-CPI-离岸-FATF-20260817.xlsx
+++ b/public/downloads/公开名单-CPI-离岸-FATF-20260817.xlsx
@@ -492,7 +492,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>来源: Transparency International — Corruption Perceptions Index 2025 (https://www.transparency.org/en/cpi/2025) · 0-100，分数越低越腐败 · 红底 = 低于建议阈值 31（待法务确认） · 抓取: 2026-08-17</t>
+          <t>来源: Transparency International — Corruption Perceptions Index 2025 (https://www.transparency.org/en/cpi/2025) · 0-100，分数越低越腐败 · 红底 = CPI ≤ 40 判为高风险（法务确认口径，0803 需求表） · 抓取: 2026-08-17</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -517,7 +517,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>≥/&lt; 阈值31</t>
+          <t>≤/&gt; 阈值40</t>
         </is>
       </c>
     </row>
@@ -1684,648 +1684,832 @@
       <c r="D85" s="5" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="4" t="n">
+      <c r="A86" s="6" t="n">
         <v>84</v>
       </c>
-      <c r="B86" s="5" t="inlineStr">
+      <c r="B86" s="7" t="inlineStr">
         <is>
           <t>Bulgaria</t>
         </is>
       </c>
-      <c r="C86" s="4" t="n">
+      <c r="C86" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="D86" s="5" t="n"/>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" s="4" t="n">
+      <c r="A87" s="6" t="n">
         <v>84</v>
       </c>
-      <c r="B87" s="5" t="inlineStr">
+      <c r="B87" s="7" t="inlineStr">
         <is>
           <t>Burkina Faso</t>
         </is>
       </c>
-      <c r="C87" s="4" t="n">
+      <c r="C87" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="D87" s="5" t="n"/>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" s="4" t="n">
+      <c r="A88" s="6" t="n">
         <v>84</v>
       </c>
-      <c r="B88" s="5" t="inlineStr">
+      <c r="B88" s="7" t="inlineStr">
         <is>
           <t>Cuba</t>
         </is>
       </c>
-      <c r="C88" s="4" t="n">
+      <c r="C88" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="D88" s="5" t="n"/>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="89">
-      <c r="A89" s="4" t="n">
+      <c r="A89" s="6" t="n">
         <v>84</v>
       </c>
-      <c r="B89" s="5" t="inlineStr">
+      <c r="B89" s="7" t="inlineStr">
         <is>
           <t>Guyana</t>
         </is>
       </c>
-      <c r="C89" s="4" t="n">
+      <c r="C89" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="D89" s="5" t="n"/>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" s="4" t="n">
+      <c r="A90" s="6" t="n">
         <v>84</v>
       </c>
-      <c r="B90" s="5" t="inlineStr">
+      <c r="B90" s="7" t="inlineStr">
         <is>
           <t>Hungary</t>
         </is>
       </c>
-      <c r="C90" s="4" t="n">
+      <c r="C90" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="D90" s="5" t="n"/>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" s="4" t="n">
+      <c r="A91" s="6" t="n">
         <v>84</v>
       </c>
-      <c r="B91" s="5" t="inlineStr">
+      <c r="B91" s="7" t="inlineStr">
         <is>
           <t>North Macedonia</t>
         </is>
       </c>
-      <c r="C91" s="4" t="n">
+      <c r="C91" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="D91" s="5" t="n"/>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" s="4" t="n">
+      <c r="A92" s="6" t="n">
         <v>84</v>
       </c>
-      <c r="B92" s="5" t="inlineStr">
+      <c r="B92" s="7" t="inlineStr">
         <is>
           <t>Tanzania</t>
         </is>
       </c>
-      <c r="C92" s="4" t="n">
+      <c r="C92" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="D92" s="5" t="n"/>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="93">
-      <c r="A93" s="4" t="n">
+      <c r="A93" s="6" t="n">
         <v>91</v>
       </c>
-      <c r="B93" s="5" t="inlineStr">
+      <c r="B93" s="7" t="inlineStr">
         <is>
           <t>Albania</t>
         </is>
       </c>
-      <c r="C93" s="4" t="n">
+      <c r="C93" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="D93" s="5" t="n"/>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" s="4" t="n">
+      <c r="A94" s="6" t="n">
         <v>91</v>
       </c>
-      <c r="B94" s="5" t="inlineStr">
+      <c r="B94" s="7" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="C94" s="4" t="n">
+      <c r="C94" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="D94" s="5" t="n"/>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="95">
-      <c r="A95" s="4" t="n">
+      <c r="A95" s="6" t="n">
         <v>91</v>
       </c>
-      <c r="B95" s="5" t="inlineStr">
+      <c r="B95" s="7" t="inlineStr">
         <is>
           <t>Maldives</t>
         </is>
       </c>
-      <c r="C95" s="4" t="n">
+      <c r="C95" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="D95" s="5" t="n"/>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="96">
-      <c r="A96" s="4" t="n">
+      <c r="A96" s="6" t="n">
         <v>91</v>
       </c>
-      <c r="B96" s="5" t="inlineStr">
+      <c r="B96" s="7" t="inlineStr">
         <is>
           <t>Morocco</t>
         </is>
       </c>
-      <c r="C96" s="4" t="n">
+      <c r="C96" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="D96" s="5" t="n"/>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" s="4" t="n">
+      <c r="A97" s="6" t="n">
         <v>91</v>
       </c>
-      <c r="B97" s="5" t="inlineStr">
+      <c r="B97" s="7" t="inlineStr">
         <is>
           <t>Tunisia</t>
         </is>
       </c>
-      <c r="C97" s="4" t="n">
+      <c r="C97" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="D97" s="5" t="n"/>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="98">
-      <c r="A98" s="4" t="n">
+      <c r="A98" s="6" t="n">
         <v>96</v>
       </c>
-      <c r="B98" s="5" t="inlineStr">
+      <c r="B98" s="7" t="inlineStr">
         <is>
           <t>Ethiopia</t>
         </is>
       </c>
-      <c r="C98" s="4" t="n">
+      <c r="C98" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="D98" s="5" t="n"/>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" s="4" t="n">
+      <c r="A99" s="6" t="n">
         <v>96</v>
       </c>
-      <c r="B99" s="5" t="inlineStr">
+      <c r="B99" s="7" t="inlineStr">
         <is>
           <t>Kazakhstan</t>
         </is>
       </c>
-      <c r="C99" s="4" t="n">
+      <c r="C99" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="D99" s="5" t="n"/>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" s="4" t="n">
+      <c r="A100" s="6" t="n">
         <v>96</v>
       </c>
-      <c r="B100" s="5" t="inlineStr">
+      <c r="B100" s="7" t="inlineStr">
         <is>
           <t>Suriname</t>
         </is>
       </c>
-      <c r="C100" s="4" t="n">
+      <c r="C100" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="D100" s="5" t="n"/>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" s="4" t="n">
+      <c r="A101" s="6" t="n">
         <v>99</v>
       </c>
-      <c r="B101" s="5" t="inlineStr">
+      <c r="B101" s="7" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
       </c>
-      <c r="C101" s="4" t="n">
+      <c r="C101" s="6" t="n">
         <v>37</v>
       </c>
-      <c r="D101" s="5" t="n"/>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" s="4" t="n">
+      <c r="A102" s="6" t="n">
         <v>99</v>
       </c>
-      <c r="B102" s="5" t="inlineStr">
+      <c r="B102" s="7" t="inlineStr">
         <is>
           <t>Dominican Republic</t>
         </is>
       </c>
-      <c r="C102" s="4" t="n">
+      <c r="C102" s="6" t="n">
         <v>37</v>
       </c>
-      <c r="D102" s="5" t="n"/>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="103">
-      <c r="A103" s="4" t="n">
+      <c r="A103" s="6" t="n">
         <v>99</v>
       </c>
-      <c r="B103" s="5" t="inlineStr">
+      <c r="B103" s="7" t="inlineStr">
         <is>
           <t>Gambia</t>
         </is>
       </c>
-      <c r="C103" s="4" t="n">
+      <c r="C103" s="6" t="n">
         <v>37</v>
       </c>
-      <c r="D103" s="5" t="n"/>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="104">
-      <c r="A104" s="4" t="n">
+      <c r="A104" s="6" t="n">
         <v>99</v>
       </c>
-      <c r="B104" s="5" t="inlineStr">
+      <c r="B104" s="7" t="inlineStr">
         <is>
           <t>Lesotho</t>
         </is>
       </c>
-      <c r="C104" s="4" t="n">
+      <c r="C104" s="6" t="n">
         <v>37</v>
       </c>
-      <c r="D104" s="5" t="n"/>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="105">
-      <c r="A105" s="4" t="n">
+      <c r="A105" s="6" t="n">
         <v>99</v>
       </c>
-      <c r="B105" s="5" t="inlineStr">
+      <c r="B105" s="7" t="inlineStr">
         <is>
           <t>Zambia</t>
         </is>
       </c>
-      <c r="C105" s="4" t="n">
+      <c r="C105" s="6" t="n">
         <v>37</v>
       </c>
-      <c r="D105" s="5" t="n"/>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="106">
-      <c r="A106" s="4" t="n">
+      <c r="A106" s="6" t="n">
         <v>104</v>
       </c>
-      <c r="B106" s="5" t="inlineStr">
+      <c r="B106" s="7" t="inlineStr">
         <is>
           <t>Argentina</t>
         </is>
       </c>
-      <c r="C106" s="4" t="n">
+      <c r="C106" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="D106" s="5" t="n"/>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="107">
-      <c r="A107" s="4" t="n">
+      <c r="A107" s="6" t="n">
         <v>104</v>
       </c>
-      <c r="B107" s="5" t="inlineStr">
+      <c r="B107" s="7" t="inlineStr">
         <is>
           <t>Belize</t>
         </is>
       </c>
-      <c r="C107" s="4" t="n">
+      <c r="C107" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="D107" s="5" t="n"/>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="108">
-      <c r="A108" s="4" t="n">
+      <c r="A108" s="6" t="n">
         <v>104</v>
       </c>
-      <c r="B108" s="5" t="inlineStr">
+      <c r="B108" s="7" t="inlineStr">
         <is>
           <t>Ukraine</t>
         </is>
       </c>
-      <c r="C108" s="4" t="n">
+      <c r="C108" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="D108" s="5" t="n"/>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="109">
-      <c r="A109" s="4" t="n">
+      <c r="A109" s="6" t="n">
         <v>107</v>
       </c>
-      <c r="B109" s="5" t="inlineStr">
+      <c r="B109" s="7" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="C109" s="4" t="n">
+      <c r="C109" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="D109" s="5" t="n"/>
+      <c r="D109" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="110">
-      <c r="A110" s="4" t="n">
+      <c r="A110" s="6" t="n">
         <v>107</v>
       </c>
-      <c r="B110" s="5" t="inlineStr">
+      <c r="B110" s="7" t="inlineStr">
         <is>
           <t>Sri Lanka</t>
         </is>
       </c>
-      <c r="C110" s="4" t="n">
+      <c r="C110" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="D110" s="5" t="n"/>
+      <c r="D110" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="111">
-      <c r="A111" s="4" t="n">
+      <c r="A111" s="6" t="n">
         <v>109</v>
       </c>
-      <c r="B111" s="5" t="inlineStr">
+      <c r="B111" s="7" t="inlineStr">
         <is>
           <t>Algeria</t>
         </is>
       </c>
-      <c r="C111" s="4" t="n">
+      <c r="C111" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="D111" s="5" t="n"/>
+      <c r="D111" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="112">
-      <c r="A112" s="4" t="n">
+      <c r="A112" s="6" t="n">
         <v>109</v>
       </c>
-      <c r="B112" s="5" t="inlineStr">
+      <c r="B112" s="7" t="inlineStr">
         <is>
           <t>Bosnia and Herzegovina</t>
         </is>
       </c>
-      <c r="C112" s="4" t="n">
+      <c r="C112" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="D112" s="5" t="n"/>
+      <c r="D112" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="113">
-      <c r="A113" s="4" t="n">
+      <c r="A113" s="6" t="n">
         <v>109</v>
       </c>
-      <c r="B113" s="5" t="inlineStr">
+      <c r="B113" s="7" t="inlineStr">
         <is>
           <t>Indonesia</t>
         </is>
       </c>
-      <c r="C113" s="4" t="n">
+      <c r="C113" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="D113" s="5" t="n"/>
+      <c r="D113" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="114">
-      <c r="A114" s="4" t="n">
+      <c r="A114" s="6" t="n">
         <v>109</v>
       </c>
-      <c r="B114" s="5" t="inlineStr">
+      <c r="B114" s="7" t="inlineStr">
         <is>
           <t>Laos</t>
         </is>
       </c>
-      <c r="C114" s="4" t="n">
+      <c r="C114" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="D114" s="5" t="n"/>
+      <c r="D114" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="115">
-      <c r="A115" s="4" t="n">
+      <c r="A115" s="6" t="n">
         <v>109</v>
       </c>
-      <c r="B115" s="5" t="inlineStr">
+      <c r="B115" s="7" t="inlineStr">
         <is>
           <t>Malawi</t>
         </is>
       </c>
-      <c r="C115" s="4" t="n">
+      <c r="C115" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="D115" s="5" t="n"/>
+      <c r="D115" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="116">
-      <c r="A116" s="4" t="n">
+      <c r="A116" s="6" t="n">
         <v>109</v>
       </c>
-      <c r="B116" s="5" t="inlineStr">
+      <c r="B116" s="7" t="inlineStr">
         <is>
           <t>Nepal</t>
         </is>
       </c>
-      <c r="C116" s="4" t="n">
+      <c r="C116" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="D116" s="5" t="n"/>
+      <c r="D116" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="117">
-      <c r="A117" s="4" t="n">
+      <c r="A117" s="6" t="n">
         <v>109</v>
       </c>
-      <c r="B117" s="5" t="inlineStr">
+      <c r="B117" s="7" t="inlineStr">
         <is>
           <t>Sierra Leone</t>
         </is>
       </c>
-      <c r="C117" s="4" t="n">
+      <c r="C117" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="D117" s="5" t="n"/>
+      <c r="D117" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="118">
-      <c r="A118" s="4" t="n">
+      <c r="A118" s="6" t="n">
         <v>116</v>
       </c>
-      <c r="B118" s="5" t="inlineStr">
+      <c r="B118" s="7" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="C118" s="4" t="n">
+      <c r="C118" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="D118" s="5" t="n"/>
+      <c r="D118" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="119">
-      <c r="A119" s="4" t="n">
+      <c r="A119" s="6" t="n">
         <v>116</v>
       </c>
-      <c r="B119" s="5" t="inlineStr">
+      <c r="B119" s="7" t="inlineStr">
         <is>
           <t>Panama</t>
         </is>
       </c>
-      <c r="C119" s="4" t="n">
+      <c r="C119" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="D119" s="5" t="n"/>
+      <c r="D119" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="120">
-      <c r="A120" s="4" t="n">
+      <c r="A120" s="6" t="n">
         <v>116</v>
       </c>
-      <c r="B120" s="5" t="inlineStr">
+      <c r="B120" s="7" t="inlineStr">
         <is>
           <t>Serbia</t>
         </is>
       </c>
-      <c r="C120" s="4" t="n">
+      <c r="C120" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="D120" s="5" t="n"/>
+      <c r="D120" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="121">
-      <c r="A121" s="4" t="n">
+      <c r="A121" s="6" t="n">
         <v>116</v>
       </c>
-      <c r="B121" s="5" t="inlineStr">
+      <c r="B121" s="7" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="C121" s="4" t="n">
+      <c r="C121" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="D121" s="5" t="n"/>
+      <c r="D121" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="122">
-      <c r="A122" s="4" t="n">
+      <c r="A122" s="6" t="n">
         <v>120</v>
       </c>
-      <c r="B122" s="5" t="inlineStr">
+      <c r="B122" s="7" t="inlineStr">
         <is>
           <t>Angola</t>
         </is>
       </c>
-      <c r="C122" s="4" t="n">
+      <c r="C122" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="D122" s="5" t="n"/>
+      <c r="D122" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="123">
-      <c r="A123" s="4" t="n">
+      <c r="A123" s="6" t="n">
         <v>120</v>
       </c>
-      <c r="B123" s="5" t="inlineStr">
+      <c r="B123" s="7" t="inlineStr">
         <is>
           <t>El Salvador</t>
         </is>
       </c>
-      <c r="C123" s="4" t="n">
+      <c r="C123" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="D123" s="5" t="n"/>
+      <c r="D123" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="124">
-      <c r="A124" s="4" t="n">
+      <c r="A124" s="6" t="n">
         <v>120</v>
       </c>
-      <c r="B124" s="5" t="inlineStr">
+      <c r="B124" s="7" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="C124" s="4" t="n">
+      <c r="C124" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="D124" s="5" t="n"/>
+      <c r="D124" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="125">
-      <c r="A125" s="4" t="n">
+      <c r="A125" s="6" t="n">
         <v>120</v>
       </c>
-      <c r="B125" s="5" t="inlineStr">
+      <c r="B125" s="7" t="inlineStr">
         <is>
           <t>Togo</t>
         </is>
       </c>
-      <c r="C125" s="4" t="n">
+      <c r="C125" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="D125" s="5" t="n"/>
+      <c r="D125" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="126">
-      <c r="A126" s="4" t="n">
+      <c r="A126" s="6" t="n">
         <v>124</v>
       </c>
-      <c r="B126" s="5" t="inlineStr">
+      <c r="B126" s="7" t="inlineStr">
         <is>
           <t>Belarus</t>
         </is>
       </c>
-      <c r="C126" s="4" t="n">
+      <c r="C126" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="D126" s="5" t="n"/>
+      <c r="D126" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="127">
-      <c r="A127" s="4" t="n">
+      <c r="A127" s="6" t="n">
         <v>124</v>
       </c>
-      <c r="B127" s="5" t="inlineStr">
+      <c r="B127" s="7" t="inlineStr">
         <is>
           <t>Djibouti</t>
         </is>
       </c>
-      <c r="C127" s="4" t="n">
+      <c r="C127" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="D127" s="5" t="n"/>
+      <c r="D127" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="128">
-      <c r="A128" s="4" t="n">
+      <c r="A128" s="6" t="n">
         <v>124</v>
       </c>
-      <c r="B128" s="5" t="inlineStr">
+      <c r="B128" s="7" t="inlineStr">
         <is>
           <t>Mongolia</t>
         </is>
       </c>
-      <c r="C128" s="4" t="n">
+      <c r="C128" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="D128" s="5" t="n"/>
+      <c r="D128" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="129">
-      <c r="A129" s="4" t="n">
+      <c r="A129" s="6" t="n">
         <v>124</v>
       </c>
-      <c r="B129" s="5" t="inlineStr">
+      <c r="B129" s="7" t="inlineStr">
         <is>
           <t>Niger</t>
         </is>
       </c>
-      <c r="C129" s="4" t="n">
+      <c r="C129" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="D129" s="5" t="n"/>
+      <c r="D129" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="130">
-      <c r="A130" s="4" t="n">
+      <c r="A130" s="6" t="n">
         <v>124</v>
       </c>
-      <c r="B130" s="5" t="inlineStr">
+      <c r="B130" s="7" t="inlineStr">
         <is>
           <t>Turkey</t>
         </is>
       </c>
-      <c r="C130" s="4" t="n">
+      <c r="C130" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="D130" s="5" t="n"/>
+      <c r="D130" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="131">
-      <c r="A131" s="4" t="n">
+      <c r="A131" s="6" t="n">
         <v>124</v>
       </c>
-      <c r="B131" s="5" t="inlineStr">
+      <c r="B131" s="7" t="inlineStr">
         <is>
           <t>Uzbekistan</t>
         </is>
       </c>
-      <c r="C131" s="4" t="n">
+      <c r="C131" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="D131" s="5" t="n"/>
+      <c r="D131" s="7" t="inlineStr">
+        <is>
+          <t>高风险 High-risk</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="6" t="n">

--- a/public/downloads/公开名单-CPI-离岸-FATF-20260817.xlsx
+++ b/public/downloads/公开名单-CPI-离岸-FATF-20260817.xlsx
@@ -3920,7 +3920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3931,7 +3931,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>来源: FATF — High-Risk Jurisdictions subject to a Call for Action(黑) / Jurisdictions under Increased Monitoring(灰) · ⚠ 本次抓取结果不可信已忽略（同一辖区同时出现在黑灰名单: south africa, turkiye），以下为法务参考文件的基线名单，名单日期 2026-06-19，非本次抓取结果 · 抓取尝试: 2026-08-17</t>
+          <t>来源: FATF — High-Risk Jurisdictions subject to a Call for Action(黑) / Jurisdictions under Increased Monitoring(灰) · 名单日期: June 2026（每年 2/6/10 月更新，需定期刷新） · 抓取: 2026-08-17</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3962,7 +3962,7 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>Democratic People's Republic of Korea</t>
+          <t>Democratic Republic of Korea</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
@@ -3989,19 +3989,19 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>黑名单 Black</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>Myanmar</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>严重战略缺陷：强化尽调，最严重者采取反制措施</t>
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>灰名单 Grey</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Angola</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>在 FATF 监督下整改中：加强监控</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Côte d'Ivoire</t>
+          <t>Democratic Republic of the Congo</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Democratic Republic of Congo</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Lao PDR</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Lao People's Democratic Republic</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Papua New Guinea</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Papua New Guinea</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Virgin Islands (UK)</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -4353,27 +4353,10 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Virgin Islands (UK)</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>在 FATF 监督下整改中：加强监控</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>灰名单 Grey</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>Yemen</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>在 FATF 监督下整改中：加强监控</t>
         </is>

--- a/public/downloads/公开名单-CPI-离岸-FATF-20260817.xlsx
+++ b/public/downloads/公开名单-CPI-离岸-FATF-20260817.xlsx
@@ -3920,7 +3920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3989,19 +3989,19 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>灰名单 Grey</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Angola</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>在 FATF 监督下整改中：加强监控</t>
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>黑名单 Black</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Myanmar</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>严重战略缺陷：强化尽调，最严重者采取反制措施</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Côte d'Ivoire</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Democratic Republic of the Congo</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Democratic Republic of the Congo</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Lao PDR</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Lao PDR</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Papua New Guinea</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Papua New Guinea</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Virgin Islands (UK)</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -4353,10 +4353,27 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
+          <t>Virgin Islands (UK)</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>在 FATF 监督下整改中：加强监控</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>灰名单 Grey</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
           <t>Yemen</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>在 FATF 监督下整改中：加强监控</t>
         </is>

--- a/public/downloads/公开名单-CPI-离岸-FATF-20260817.xlsx
+++ b/public/downloads/公开名单-CPI-离岸-FATF-20260817.xlsx
@@ -492,7 +492,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>来源: Transparency International — Corruption Perceptions Index 2025 (https://www.transparency.org/en/cpi/2025) · 0-100，分数越低越腐败 · 红底 = CPI ≤ 40 判为高风险（法务确认口径，0803 需求表） · 抓取: 2026-08-17</t>
+          <t>来源: Transparency International — Corruption Perceptions Index 2025 (https://www.transparency.org/en/cpi/2025) · 0-100，分数越低越腐败 · 红底 = CPI ≤ 40 判为高风险（法务确认口径，0803 需求表） · 数据来源: 法务确认（xujz · 2026-08-17 20:31） · 2026-08-17</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -527,11 +527,11 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>denmark</t>
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D3" s="5" t="n"/>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>finland</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
@@ -555,7 +555,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>singapore</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
@@ -569,7 +569,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>new zealand</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
@@ -579,11 +579,11 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>norway</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
@@ -597,7 +597,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>sweden</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
@@ -607,11 +607,11 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>switzerland</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
@@ -625,7 +625,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>luxembourg</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
@@ -635,11 +635,11 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>netherlands</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
@@ -653,7 +653,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>germany</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
@@ -663,11 +663,11 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>iceland</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
@@ -681,7 +681,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>australia</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
@@ -691,11 +691,11 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>estonia</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
@@ -705,11 +705,11 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>hong kong</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
@@ -719,11 +719,11 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>ireland</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
@@ -737,7 +737,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>canada</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
@@ -751,7 +751,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>uruguay</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
@@ -765,7 +765,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Bhutan</t>
+          <t>bhutan</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
@@ -775,11 +775,11 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>japan</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
@@ -793,7 +793,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>united kingdom</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
@@ -807,7 +807,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>austria</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
@@ -817,11 +817,11 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>belgium</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
@@ -831,11 +831,11 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>united arab emirates</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
@@ -849,7 +849,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Barbados</t>
+          <t>barbados</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
@@ -859,11 +859,11 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Seychelles</t>
+          <t>seychelles</t>
         </is>
       </c>
       <c r="C27" s="4" t="n">
@@ -873,11 +873,11 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>taiwan</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>france</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
@@ -905,7 +905,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>lithuania</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
@@ -919,7 +919,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Bahamas</t>
+          <t>bahamas</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
@@ -929,11 +929,11 @@
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>united states of america</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
@@ -947,7 +947,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Brunei Darussalam</t>
+          <t>brunei darussalam</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
@@ -957,11 +957,11 @@
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>chile</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
@@ -971,11 +971,11 @@
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Korea, South</t>
+          <t>saint vincent and the grenadines</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
@@ -985,11 +985,11 @@
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Saint Vincent and the Grenadines</t>
+          <t>south korea</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>cabo verde</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
@@ -1013,11 +1013,11 @@
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>israel</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Dominica</t>
+          <t>dominica</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
@@ -1041,11 +1041,11 @@
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>latvia</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>czechia</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
@@ -1069,11 +1069,11 @@
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Saint Lucia</t>
+          <t>saint lucia</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>botswana</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
@@ -1097,11 +1097,11 @@
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>qatar</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
@@ -1111,11 +1111,11 @@
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>rwanda</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
@@ -1125,11 +1125,11 @@
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>slovenia</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>saudi arabia</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Costa Rica</t>
+          <t>costa rica</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
@@ -1167,11 +1167,11 @@
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Grenada</t>
+          <t>grenada</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
@@ -1181,11 +1181,11 @@
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>portugal</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>cyprus</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
@@ -1209,11 +1209,11 @@
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>Fiji</t>
+          <t>fiji</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
@@ -1223,11 +1223,11 @@
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>spain</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>italy</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
@@ -1251,11 +1251,11 @@
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>poland</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>malaysia</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
@@ -1279,11 +1279,11 @@
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>oman</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>Bahrain</t>
+          <t>bahrain</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
@@ -1307,11 +1307,11 @@
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>georgia</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
@@ -1321,11 +1321,11 @@
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>greece</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
@@ -1335,11 +1335,11 @@
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>jordan</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>malta</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Mauritius</t>
+          <t>mauritius</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
@@ -1377,11 +1377,11 @@
     </row>
     <row r="64">
       <c r="A64" s="4" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>slovakia</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>croatia</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
@@ -1405,11 +1405,11 @@
     </row>
     <row r="66">
       <c r="A66" s="4" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>Vanuatu</t>
+          <t>vanuatu</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>armenia</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
@@ -1433,11 +1433,11 @@
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>kuwait</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
@@ -1447,11 +1447,11 @@
     </row>
     <row r="69">
       <c r="A69" s="4" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>Montenegro</t>
+          <t>montenegro</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
@@ -1461,11 +1461,11 @@
     </row>
     <row r="70">
       <c r="A70" s="4" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>namibia</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
@@ -1475,11 +1475,11 @@
     </row>
     <row r="71">
       <c r="A71" s="4" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>senegal</t>
         </is>
       </c>
       <c r="C71" s="4" t="n">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>benin</t>
         </is>
       </c>
       <c r="C72" s="4" t="n">
@@ -1503,11 +1503,11 @@
     </row>
     <row r="73">
       <c r="A73" s="4" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>romania</t>
         </is>
       </c>
       <c r="C73" s="4" t="n">
@@ -1517,11 +1517,11 @@
     </row>
     <row r="74">
       <c r="A74" s="4" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>Sao Tome and Principe</t>
+          <t>sao tome and principe</t>
         </is>
       </c>
       <c r="C74" s="4" t="n">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Jamaica</t>
+          <t>jamaica</t>
         </is>
       </c>
       <c r="C75" s="4" t="n">
@@ -1545,11 +1545,11 @@
     </row>
     <row r="76">
       <c r="A76" s="4" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>Solomon Islands</t>
+          <t>solomon islands</t>
         </is>
       </c>
       <c r="C76" s="4" t="n">
@@ -1559,11 +1559,11 @@
     </row>
     <row r="77">
       <c r="A77" s="4" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>Timor-Leste</t>
+          <t>timor leste</t>
         </is>
       </c>
       <c r="C77" s="4" t="n">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>china</t>
         </is>
       </c>
       <c r="C78" s="4" t="n">
@@ -1587,11 +1587,11 @@
     </row>
     <row r="79">
       <c r="A79" s="4" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>Cote d'Ivoire</t>
+          <t>cote divoire</t>
         </is>
       </c>
       <c r="C79" s="4" t="n">
@@ -1601,11 +1601,11 @@
     </row>
     <row r="80">
       <c r="A80" s="4" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>ghana</t>
         </is>
       </c>
       <c r="C80" s="4" t="n">
@@ -1615,11 +1615,11 @@
     </row>
     <row r="81">
       <c r="A81" s="4" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>Kosovo</t>
+          <t>kosovo</t>
         </is>
       </c>
       <c r="C81" s="4" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>Moldova</t>
+          <t>moldova</t>
         </is>
       </c>
       <c r="C82" s="4" t="n">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>south africa</t>
         </is>
       </c>
       <c r="C83" s="4" t="n">
@@ -1657,11 +1657,11 @@
     </row>
     <row r="84">
       <c r="A84" s="4" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>Trinidad and Tobago</t>
+          <t>trinidad and tobago</t>
         </is>
       </c>
       <c r="C84" s="4" t="n">
@@ -1671,11 +1671,11 @@
     </row>
     <row r="85">
       <c r="A85" s="4" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>vietnam</t>
         </is>
       </c>
       <c r="C85" s="4" t="n">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>bulgaria</t>
         </is>
       </c>
       <c r="C86" s="6" t="n">
@@ -1703,11 +1703,11 @@
     </row>
     <row r="87">
       <c r="A87" s="6" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>Burkina Faso</t>
+          <t>burkina faso</t>
         </is>
       </c>
       <c r="C87" s="6" t="n">
@@ -1721,11 +1721,11 @@
     </row>
     <row r="88">
       <c r="A88" s="6" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>Cuba</t>
+          <t>cuba</t>
         </is>
       </c>
       <c r="C88" s="6" t="n">
@@ -1739,11 +1739,11 @@
     </row>
     <row r="89">
       <c r="A89" s="6" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>guyana</t>
         </is>
       </c>
       <c r="C89" s="6" t="n">
@@ -1757,11 +1757,11 @@
     </row>
     <row r="90">
       <c r="A90" s="6" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>hungary</t>
         </is>
       </c>
       <c r="C90" s="6" t="n">
@@ -1775,11 +1775,11 @@
     </row>
     <row r="91">
       <c r="A91" s="6" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>North Macedonia</t>
+          <t>north macedonia</t>
         </is>
       </c>
       <c r="C91" s="6" t="n">
@@ -1793,11 +1793,11 @@
     </row>
     <row r="92">
       <c r="A92" s="6" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>tanzania</t>
         </is>
       </c>
       <c r="C92" s="6" t="n">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="B93" s="7" t="inlineStr">
         <is>
-          <t>Albania</t>
+          <t>albania</t>
         </is>
       </c>
       <c r="C93" s="6" t="n">
@@ -1829,11 +1829,11 @@
     </row>
     <row r="94">
       <c r="A94" s="6" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>india</t>
         </is>
       </c>
       <c r="C94" s="6" t="n">
@@ -1847,11 +1847,11 @@
     </row>
     <row r="95">
       <c r="A95" s="6" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>Maldives</t>
+          <t>maldives</t>
         </is>
       </c>
       <c r="C95" s="6" t="n">
@@ -1865,11 +1865,11 @@
     </row>
     <row r="96">
       <c r="A96" s="6" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>morocco</t>
         </is>
       </c>
       <c r="C96" s="6" t="n">
@@ -1883,11 +1883,11 @@
     </row>
     <row r="97">
       <c r="A97" s="6" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B97" s="7" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>tunisia</t>
         </is>
       </c>
       <c r="C97" s="6" t="n">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>ethiopia</t>
         </is>
       </c>
       <c r="C98" s="6" t="n">
@@ -1919,11 +1919,11 @@
     </row>
     <row r="99">
       <c r="A99" s="6" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>kazakhstan</t>
         </is>
       </c>
       <c r="C99" s="6" t="n">
@@ -1937,11 +1937,11 @@
     </row>
     <row r="100">
       <c r="A100" s="6" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>Suriname</t>
+          <t>suriname</t>
         </is>
       </c>
       <c r="C100" s="6" t="n">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="B101" s="7" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>colombia</t>
         </is>
       </c>
       <c r="C101" s="6" t="n">
@@ -1973,11 +1973,11 @@
     </row>
     <row r="102">
       <c r="A102" s="6" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>dominican republic</t>
         </is>
       </c>
       <c r="C102" s="6" t="n">
@@ -1991,11 +1991,11 @@
     </row>
     <row r="103">
       <c r="A103" s="6" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B103" s="7" t="inlineStr">
         <is>
-          <t>Gambia</t>
+          <t>gambia</t>
         </is>
       </c>
       <c r="C103" s="6" t="n">
@@ -2009,11 +2009,11 @@
     </row>
     <row r="104">
       <c r="A104" s="6" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>lesotho</t>
         </is>
       </c>
       <c r="C104" s="6" t="n">
@@ -2027,11 +2027,11 @@
     </row>
     <row r="105">
       <c r="A105" s="6" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B105" s="7" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>zambia</t>
         </is>
       </c>
       <c r="C105" s="6" t="n">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>argentina</t>
         </is>
       </c>
       <c r="C106" s="6" t="n">
@@ -2063,11 +2063,11 @@
     </row>
     <row r="107">
       <c r="A107" s="6" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B107" s="7" t="inlineStr">
         <is>
-          <t>Belize</t>
+          <t>belize</t>
         </is>
       </c>
       <c r="C107" s="6" t="n">
@@ -2081,11 +2081,11 @@
     </row>
     <row r="108">
       <c r="A108" s="6" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B108" s="7" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>ukraine</t>
         </is>
       </c>
       <c r="C108" s="6" t="n">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="B109" s="7" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>brazil</t>
         </is>
       </c>
       <c r="C109" s="6" t="n">
@@ -2117,11 +2117,11 @@
     </row>
     <row r="110">
       <c r="A110" s="6" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B110" s="7" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>sri lanka</t>
         </is>
       </c>
       <c r="C110" s="6" t="n">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="B111" s="7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>algeria</t>
         </is>
       </c>
       <c r="C111" s="6" t="n">
@@ -2153,11 +2153,11 @@
     </row>
     <row r="112">
       <c r="A112" s="6" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B112" s="7" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>bosnia and herzegovina</t>
         </is>
       </c>
       <c r="C112" s="6" t="n">
@@ -2171,11 +2171,11 @@
     </row>
     <row r="113">
       <c r="A113" s="6" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B113" s="7" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>indonesia</t>
         </is>
       </c>
       <c r="C113" s="6" t="n">
@@ -2189,11 +2189,11 @@
     </row>
     <row r="114">
       <c r="A114" s="6" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B114" s="7" t="inlineStr">
         <is>
-          <t>Laos</t>
+          <t>laos</t>
         </is>
       </c>
       <c r="C114" s="6" t="n">
@@ -2207,11 +2207,11 @@
     </row>
     <row r="115">
       <c r="A115" s="6" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B115" s="7" t="inlineStr">
         <is>
-          <t>Malawi</t>
+          <t>malawi</t>
         </is>
       </c>
       <c r="C115" s="6" t="n">
@@ -2225,11 +2225,11 @@
     </row>
     <row r="116">
       <c r="A116" s="6" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B116" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>nepal</t>
         </is>
       </c>
       <c r="C116" s="6" t="n">
@@ -2243,11 +2243,11 @@
     </row>
     <row r="117">
       <c r="A117" s="6" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B117" s="7" t="inlineStr">
         <is>
-          <t>Sierra Leone</t>
+          <t>sierra leone</t>
         </is>
       </c>
       <c r="C117" s="6" t="n">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="B118" s="7" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>ecuador</t>
         </is>
       </c>
       <c r="C118" s="6" t="n">
@@ -2279,11 +2279,11 @@
     </row>
     <row r="119">
       <c r="A119" s="6" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B119" s="7" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>panama</t>
         </is>
       </c>
       <c r="C119" s="6" t="n">
@@ -2297,11 +2297,11 @@
     </row>
     <row r="120">
       <c r="A120" s="6" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B120" s="7" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>serbia</t>
         </is>
       </c>
       <c r="C120" s="6" t="n">
@@ -2315,11 +2315,11 @@
     </row>
     <row r="121">
       <c r="A121" s="6" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B121" s="7" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>thailand</t>
         </is>
       </c>
       <c r="C121" s="6" t="n">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="B122" s="7" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>angola</t>
         </is>
       </c>
       <c r="C122" s="6" t="n">
@@ -2351,11 +2351,11 @@
     </row>
     <row r="123">
       <c r="A123" s="6" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B123" s="7" t="inlineStr">
         <is>
-          <t>El Salvador</t>
+          <t>el salvador</t>
         </is>
       </c>
       <c r="C123" s="6" t="n">
@@ -2369,11 +2369,11 @@
     </row>
     <row r="124">
       <c r="A124" s="6" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B124" s="7" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>philippines</t>
         </is>
       </c>
       <c r="C124" s="6" t="n">
@@ -2387,11 +2387,11 @@
     </row>
     <row r="125">
       <c r="A125" s="6" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B125" s="7" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>togo</t>
         </is>
       </c>
       <c r="C125" s="6" t="n">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="B126" s="7" t="inlineStr">
         <is>
-          <t>Belarus</t>
+          <t>belarus</t>
         </is>
       </c>
       <c r="C126" s="6" t="n">
@@ -2423,11 +2423,11 @@
     </row>
     <row r="127">
       <c r="A127" s="6" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B127" s="7" t="inlineStr">
         <is>
-          <t>Djibouti</t>
+          <t>djibouti</t>
         </is>
       </c>
       <c r="C127" s="6" t="n">
@@ -2441,11 +2441,11 @@
     </row>
     <row r="128">
       <c r="A128" s="6" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B128" s="7" t="inlineStr">
         <is>
-          <t>Mongolia</t>
+          <t>mongolia</t>
         </is>
       </c>
       <c r="C128" s="6" t="n">
@@ -2459,11 +2459,11 @@
     </row>
     <row r="129">
       <c r="A129" s="6" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B129" s="7" t="inlineStr">
         <is>
-          <t>Niger</t>
+          <t>niger</t>
         </is>
       </c>
       <c r="C129" s="6" t="n">
@@ -2477,11 +2477,11 @@
     </row>
     <row r="130">
       <c r="A130" s="6" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B130" s="7" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>turkey</t>
         </is>
       </c>
       <c r="C130" s="6" t="n">
@@ -2495,11 +2495,11 @@
     </row>
     <row r="131">
       <c r="A131" s="6" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B131" s="7" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>uzbekistan</t>
         </is>
       </c>
       <c r="C131" s="6" t="n">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="B132" s="7" t="inlineStr">
         <is>
-          <t>Azerbaijan</t>
+          <t>azerbaijan</t>
         </is>
       </c>
       <c r="C132" s="6" t="n">
@@ -2531,11 +2531,11 @@
     </row>
     <row r="133">
       <c r="A133" s="6" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B133" s="7" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>egypt</t>
         </is>
       </c>
       <c r="C133" s="6" t="n">
@@ -2549,11 +2549,11 @@
     </row>
     <row r="134">
       <c r="A134" s="6" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B134" s="7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>kenya</t>
         </is>
       </c>
       <c r="C134" s="6" t="n">
@@ -2567,11 +2567,11 @@
     </row>
     <row r="135">
       <c r="A135" s="6" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B135" s="7" t="inlineStr">
         <is>
-          <t>Mauritania</t>
+          <t>mauritania</t>
         </is>
       </c>
       <c r="C135" s="6" t="n">
@@ -2585,11 +2585,11 @@
     </row>
     <row r="136">
       <c r="A136" s="6" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B136" s="7" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>peru</t>
         </is>
       </c>
       <c r="C136" s="6" t="n">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="B137" s="7" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>gabon</t>
         </is>
       </c>
       <c r="C137" s="6" t="n">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="B138" s="7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>bolivia</t>
         </is>
       </c>
       <c r="C138" s="6" t="n">
@@ -2639,11 +2639,11 @@
     </row>
     <row r="139">
       <c r="A139" s="6" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B139" s="7" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>iraq</t>
         </is>
       </c>
       <c r="C139" s="6" t="n">
@@ -2657,11 +2657,11 @@
     </row>
     <row r="140">
       <c r="A140" s="6" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B140" s="7" t="inlineStr">
         <is>
-          <t>Liberia</t>
+          <t>liberia</t>
         </is>
       </c>
       <c r="C140" s="6" t="n">
@@ -2675,11 +2675,11 @@
     </row>
     <row r="141">
       <c r="A141" s="6" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B141" s="7" t="inlineStr">
         <is>
-          <t>Mali</t>
+          <t>mali</t>
         </is>
       </c>
       <c r="C141" s="6" t="n">
@@ -2693,11 +2693,11 @@
     </row>
     <row r="142">
       <c r="A142" s="6" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B142" s="7" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>pakistan</t>
         </is>
       </c>
       <c r="C142" s="6" t="n">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B143" s="7" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>mexico</t>
         </is>
       </c>
       <c r="C143" s="6" t="n">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="B144" s="7" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>cameroon</t>
         </is>
       </c>
       <c r="C144" s="6" t="n">
@@ -2747,11 +2747,11 @@
     </row>
     <row r="145">
       <c r="A145" s="6" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B145" s="7" t="inlineStr">
         <is>
-          <t>Guatemala</t>
+          <t>guatemala</t>
         </is>
       </c>
       <c r="C145" s="6" t="n">
@@ -2765,11 +2765,11 @@
     </row>
     <row r="146">
       <c r="A146" s="6" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B146" s="7" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>guinea</t>
         </is>
       </c>
       <c r="C146" s="6" t="n">
@@ -2783,11 +2783,11 @@
     </row>
     <row r="147">
       <c r="A147" s="6" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B147" s="7" t="inlineStr">
         <is>
-          <t>Kyrgyzstan</t>
+          <t>kyrgyzstan</t>
         </is>
       </c>
       <c r="C147" s="6" t="n">
@@ -2801,11 +2801,11 @@
     </row>
     <row r="148">
       <c r="A148" s="6" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B148" s="7" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>nigeria</t>
         </is>
       </c>
       <c r="C148" s="6" t="n">
@@ -2819,11 +2819,11 @@
     </row>
     <row r="149">
       <c r="A149" s="6" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B149" s="7" t="inlineStr">
         <is>
-          <t>Papua New Guinea</t>
+          <t>papua new guinea</t>
         </is>
       </c>
       <c r="C149" s="6" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="B150" s="7" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>madagascar</t>
         </is>
       </c>
       <c r="C150" s="6" t="n">
@@ -2855,11 +2855,11 @@
     </row>
     <row r="151">
       <c r="A151" s="6" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B151" s="7" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>uganda</t>
         </is>
       </c>
       <c r="C151" s="6" t="n">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="B152" s="7" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>bangladesh</t>
         </is>
       </c>
       <c r="C152" s="6" t="n">
@@ -2891,11 +2891,11 @@
     </row>
     <row r="153">
       <c r="A153" s="6" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B153" s="7" t="inlineStr">
         <is>
-          <t>Central African Republic</t>
+          <t>central african republic</t>
         </is>
       </c>
       <c r="C153" s="6" t="n">
@@ -2909,11 +2909,11 @@
     </row>
     <row r="154">
       <c r="A154" s="6" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B154" s="7" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>paraguay</t>
         </is>
       </c>
       <c r="C154" s="6" t="n">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B155" s="7" t="inlineStr">
         <is>
-          <t>Congo</t>
+          <t>congo</t>
         </is>
       </c>
       <c r="C155" s="6" t="n">
@@ -2945,11 +2945,11 @@
     </row>
     <row r="156">
       <c r="A156" s="6" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B156" s="7" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>eswatini</t>
         </is>
       </c>
       <c r="C156" s="6" t="n">
@@ -2963,11 +2963,11 @@
     </row>
     <row r="157">
       <c r="A157" s="6" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B157" s="7" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>iran</t>
         </is>
       </c>
       <c r="C157" s="6" t="n">
@@ -2981,11 +2981,11 @@
     </row>
     <row r="158">
       <c r="A158" s="6" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B158" s="7" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>lebanon</t>
         </is>
       </c>
       <c r="C158" s="6" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="B159" s="7" t="inlineStr">
         <is>
-          <t>Chad</t>
+          <t>chad</t>
         </is>
       </c>
       <c r="C159" s="6" t="n">
@@ -3017,11 +3017,11 @@
     </row>
     <row r="160">
       <c r="A160" s="6" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B160" s="7" t="inlineStr">
         <is>
-          <t>Honduras</t>
+          <t>honduras</t>
         </is>
       </c>
       <c r="C160" s="6" t="n">
@@ -3035,11 +3035,11 @@
     </row>
     <row r="161">
       <c r="A161" s="6" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B161" s="7" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>russia</t>
         </is>
       </c>
       <c r="C161" s="6" t="n">
@@ -3053,11 +3053,11 @@
     </row>
     <row r="162">
       <c r="A162" s="6" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B162" s="7" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>zimbabwe</t>
         </is>
       </c>
       <c r="C162" s="6" t="n">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="B163" s="7" t="inlineStr">
         <is>
-          <t>Guinea Bissau</t>
+          <t>guinea bissau</t>
         </is>
       </c>
       <c r="C163" s="6" t="n">
@@ -3089,11 +3089,11 @@
     </row>
     <row r="164">
       <c r="A164" s="6" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B164" s="7" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>mozambique</t>
         </is>
       </c>
       <c r="C164" s="6" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="B165" s="7" t="inlineStr">
         <is>
-          <t>Cambodia</t>
+          <t>cambodia</t>
         </is>
       </c>
       <c r="C165" s="6" t="n">
@@ -3125,11 +3125,11 @@
     </row>
     <row r="166">
       <c r="A166" s="6" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B166" s="7" t="inlineStr">
         <is>
-          <t>Comoros</t>
+          <t>comoros</t>
         </is>
       </c>
       <c r="C166" s="6" t="n">
@@ -3143,11 +3143,11 @@
     </row>
     <row r="167">
       <c r="A167" s="6" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B167" s="7" t="inlineStr">
         <is>
-          <t>Democratic Republic of the Congo</t>
+          <t>democratic republic of the congo</t>
         </is>
       </c>
       <c r="C167" s="6" t="n">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="B168" s="7" t="inlineStr">
         <is>
-          <t>Tajikistan</t>
+          <t>tajikistan</t>
         </is>
       </c>
       <c r="C168" s="6" t="n">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="B169" s="7" t="inlineStr">
         <is>
-          <t>Burundi</t>
+          <t>burundi</t>
         </is>
       </c>
       <c r="C169" s="6" t="n">
@@ -3197,11 +3197,11 @@
     </row>
     <row r="170">
       <c r="A170" s="6" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B170" s="7" t="inlineStr">
         <is>
-          <t>Turkmenistan</t>
+          <t>turkmenistan</t>
         </is>
       </c>
       <c r="C170" s="6" t="n">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="B171" s="7" t="inlineStr">
         <is>
-          <t>Afghanistan</t>
+          <t>afghanistan</t>
         </is>
       </c>
       <c r="C171" s="6" t="n">
@@ -3233,11 +3233,11 @@
     </row>
     <row r="172">
       <c r="A172" s="6" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B172" s="7" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>haiti</t>
         </is>
       </c>
       <c r="C172" s="6" t="n">
@@ -3251,11 +3251,11 @@
     </row>
     <row r="173">
       <c r="A173" s="6" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B173" s="7" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>myanmar</t>
         </is>
       </c>
       <c r="C173" s="6" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="B174" s="7" t="inlineStr">
         <is>
-          <t>Equatorial Guinea</t>
+          <t>equatorial guinea</t>
         </is>
       </c>
       <c r="C174" s="6" t="n">
@@ -3287,11 +3287,11 @@
     </row>
     <row r="175">
       <c r="A175" s="6" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B175" s="7" t="inlineStr">
         <is>
-          <t>Korea, North</t>
+          <t>north korea</t>
         </is>
       </c>
       <c r="C175" s="6" t="n">
@@ -3305,11 +3305,11 @@
     </row>
     <row r="176">
       <c r="A176" s="6" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B176" s="7" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>syria</t>
         </is>
       </c>
       <c r="C176" s="6" t="n">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="B177" s="7" t="inlineStr">
         <is>
-          <t>Nicaragua</t>
+          <t>nicaragua</t>
         </is>
       </c>
       <c r="C177" s="6" t="n">
@@ -3341,11 +3341,11 @@
     </row>
     <row r="178">
       <c r="A178" s="6" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B178" s="7" t="inlineStr">
         <is>
-          <t>Sudan</t>
+          <t>sudan</t>
         </is>
       </c>
       <c r="C178" s="6" t="n">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="B179" s="7" t="inlineStr">
         <is>
-          <t>Eritrea</t>
+          <t>eritrea</t>
         </is>
       </c>
       <c r="C179" s="6" t="n">
@@ -3377,11 +3377,11 @@
     </row>
     <row r="180">
       <c r="A180" s="6" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B180" s="7" t="inlineStr">
         <is>
-          <t>Libya</t>
+          <t>libya</t>
         </is>
       </c>
       <c r="C180" s="6" t="n">
@@ -3395,11 +3395,11 @@
     </row>
     <row r="181">
       <c r="A181" s="6" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B181" s="7" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>yemen</t>
         </is>
       </c>
       <c r="C181" s="6" t="n">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="B182" s="7" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>venezuela</t>
         </is>
       </c>
       <c r="C182" s="6" t="n">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="B183" s="7" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>somalia</t>
         </is>
       </c>
       <c r="C183" s="6" t="n">
@@ -3449,11 +3449,11 @@
     </row>
     <row r="184">
       <c r="A184" s="6" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B184" s="7" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>south sudan</t>
         </is>
       </c>
       <c r="C184" s="6" t="n">
@@ -3489,7 +3489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>来源: Eurostat Glossary — List of offshore financial centres (Balance of Payments Vademecum, Appendix 7) · 共 40 个辖区 · 抓取: 2026-08-17</t>
+          <t>来源: Eurostat Glossary — List of offshore financial centres (Balance of Payments Vademecum, Appendix 7) · 共 40 个辖区 · 数据来源: 抓取 · 2026-08-17</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3931,7 +3931,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>来源: FATF — High-Risk Jurisdictions subject to a Call for Action(黑) / Jurisdictions under Increased Monitoring(灰) · 名单日期: June 2026（每年 2/6/10 月更新，需定期刷新） · 抓取: 2026-08-17</t>
+          <t>来源: FATF — High-Risk Jurisdictions subject to a Call for Action(黑) / Jurisdictions under Increased Monitoring(灰) · 与本次官方抓取一致（同一期 2026-06），采用法务确认口径，名单日期 2026-06-19（法务维护的基线） · 抓取尝试: 2026-08-17</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
